--- a/data/trans_camb/P16A07-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A07-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 1,27</t>
+          <t>-2,21; 1,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 0,3</t>
+          <t>-2,99; 0,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 3,9</t>
+          <t>-0,24; 4,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 6,48</t>
+          <t>0,99; 6,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 5,12</t>
+          <t>-0,33; 5,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 2,93</t>
+          <t>-1,69; 2,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 3,26</t>
+          <t>0,01; 3,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 2,19</t>
+          <t>-1,05; 2,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 2,69</t>
+          <t>-0,3; 2,75</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-55,59; 60,24</t>
+          <t>-56,68; 58,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-73,29; 20,45</t>
+          <t>-72,4; 25,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 170,71</t>
+          <t>-7,93; 167,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,42; 129,42</t>
+          <t>13,13; 149,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 106,41</t>
+          <t>-5,76; 105,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,64; 64,67</t>
+          <t>-22,01; 62,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 87,44</t>
+          <t>-1,27; 86,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 58,2</t>
+          <t>-19,62; 53,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 71,01</t>
+          <t>-6,04; 71,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 2,89</t>
+          <t>-0,37; 2,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,6</t>
+          <t>-1,82; 0,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,14</t>
+          <t>-1,97; 1,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 4,05</t>
+          <t>-0,82; 4,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 3,05</t>
+          <t>-1,59; 2,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 2,09</t>
+          <t>-2,12; 1,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 2,91</t>
+          <t>0,05; 2,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 1,46</t>
+          <t>-1,17; 1,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 0,92</t>
+          <t>-2,0; 0,9</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 174,6</t>
+          <t>-13,87; 177,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-63,83; 43,2</t>
+          <t>-60,42; 42,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,76; 66,24</t>
+          <t>-62,91; 61,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 77,38</t>
+          <t>-10,57; 74,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,84; 59,6</t>
+          <t>-20,65; 57,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,79; 41,37</t>
+          <t>-25,95; 37,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 77,96</t>
+          <t>0,75; 76,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,61; 37,98</t>
+          <t>-22,98; 38,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-42,48; 23,58</t>
+          <t>-38,51; 24,27</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,35</t>
+          <t>-0,81; 2,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,99</t>
+          <t>-0,69; 2,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,55</t>
+          <t>0,44; 3,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 3,83</t>
+          <t>-1,12; 3,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 1,99</t>
+          <t>-2,57; 2,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 3,67</t>
+          <t>-3,59; 3,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 2,58</t>
+          <t>-0,37; 2,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1,63</t>
+          <t>-1,17; 1,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 3,21</t>
+          <t>-0,72; 3,17</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-43,64; 301,49</t>
+          <t>-44,07; 274,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-40,11; 236,79</t>
+          <t>-37,86; 248,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,65; 411,58</t>
+          <t>4,74; 399,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,88; 85,02</t>
+          <t>-16,75; 86,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,45; 42,44</t>
+          <t>-36,23; 48,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,46; 74,15</t>
+          <t>-50,39; 71,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 90,33</t>
+          <t>-9,64; 89,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-26,71; 54,77</t>
+          <t>-29,08; 55,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 107,83</t>
+          <t>-12,54; 102,18</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,08</t>
+          <t>0,69; 3,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 2,58</t>
+          <t>-0,09; 2,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,18</t>
+          <t>0,47; 3,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,86</t>
+          <t>-1,01; 3,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,66</t>
+          <t>-2,04; 2,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 3,66</t>
+          <t>-1,15; 3,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,28</t>
+          <t>0,32; 3,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,15</t>
+          <t>-0,62; 2,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,88</t>
+          <t>0,29; 3,06</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>24,5; 298,41</t>
+          <t>22,71; 293,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 204,38</t>
+          <t>-4,69; 217,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,34; 233,35</t>
+          <t>15,97; 253,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 63,28</t>
+          <t>-12,75; 61,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 45,88</t>
+          <t>-25,38; 41,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 62,44</t>
+          <t>-12,36; 62,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,94; 86,48</t>
+          <t>4,63; 81,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 54,38</t>
+          <t>-12,23; 51,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,08; 71,78</t>
+          <t>5,09; 77,88</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,93</t>
+          <t>0,24; 1,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,68</t>
+          <t>-0,59; 0,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,88</t>
+          <t>0,26; 1,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,07</t>
+          <t>0,67; 3,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,77</t>
+          <t>-0,56; 1,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,85</t>
+          <t>-0,9; 1,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,31</t>
+          <t>0,71; 2,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,09</t>
+          <t>-0,36; 1,05</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,71</t>
+          <t>0,1; 1,67</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5,48; 102,5</t>
+          <t>9,23; 105,17</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-27,8; 37,1</t>
+          <t>-24,77; 44,99</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7,85; 104,67</t>
+          <t>9,6; 110,28</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6,83; 52,1</t>
+          <t>9,15; 56,31</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 29,55</t>
+          <t>-7,99; 32,64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 31,16</t>
+          <t>-12,2; 31,9</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,21; 57,59</t>
+          <t>15,34; 56,44</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 27,41</t>
+          <t>-8,22; 26,14</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2,42; 43,0</t>
+          <t>2,14; 41,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A07-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A07-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>1,8</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,24</t>
+          <t>-2,26; 1,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 0,39</t>
+          <t>-2,84; 0,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 4,0</t>
+          <t>-0,3; 3,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 6,76</t>
+          <t>0,85; 6,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 5,42</t>
+          <t>-0,44; 5,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 2,96</t>
+          <t>-1,61; 2,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,01; 3,35</t>
+          <t>-0,2; 3,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,15</t>
+          <t>-1,0; 2,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,75</t>
+          <t>-0,34; 2,66</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-56,68; 58,92</t>
+          <t>-55,32; 54,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-72,4; 25,08</t>
+          <t>-71,19; 18,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 167,54</t>
+          <t>-10,63; 180,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,13; 149,44</t>
+          <t>12,24; 133,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 105,95</t>
+          <t>-6,1; 105,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,01; 62,46</t>
+          <t>-22,01; 59,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 86,49</t>
+          <t>-4,3; 80,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 53,45</t>
+          <t>-19,99; 57,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 71,54</t>
+          <t>-6,33; 68,29</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>0,1</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,89</t>
+          <t>-0,25; 2,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,69</t>
+          <t>-1,8; 0,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,11</t>
+          <t>-1,17; 1,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 4,03</t>
+          <t>-0,76; 4,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,98</t>
+          <t>-1,68; 3,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,95</t>
+          <t>-2,1; 2,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,8</t>
+          <t>0,02; 2,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,43</t>
+          <t>-1,23; 1,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,9</t>
+          <t>-1,21; 1,33</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-11,11%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>-0,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-8,15%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 177,58</t>
+          <t>-11,09; 172,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-60,42; 42,98</t>
+          <t>-63,81; 44,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-62,91; 61,12</t>
+          <t>-40,4; 104,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 74,09</t>
+          <t>-12,55; 75,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,65; 57,67</t>
+          <t>-21,2; 56,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,95; 37,71</t>
+          <t>-28,06; 40,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 76,67</t>
+          <t>0,13; 75,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,98; 38,08</t>
+          <t>-25,61; 42,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-38,51; 24,27</t>
+          <t>-22,81; 37,44</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,9</t>
+          <t>1,91</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>2,54</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,58</t>
+          <t>2,23</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,35</t>
+          <t>-0,77; 2,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,12</t>
+          <t>-0,73; 2,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,82</t>
+          <t>0,46; 3,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,93</t>
+          <t>-1,19; 3,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 2,22</t>
+          <t>-2,78; 2,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 3,63</t>
+          <t>-0,1; 4,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,66</t>
+          <t>-0,46; 2,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,67</t>
+          <t>-1,2; 1,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 3,17</t>
+          <t>0,92; 3,73</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132,79%</t>
+          <t>133,55%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>61,98%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-44,07; 274,61</t>
+          <t>-47,21; 252,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-37,86; 248,4</t>
+          <t>-39,41; 223,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,74; 399,8</t>
+          <t>14,83; 407,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 86,8</t>
+          <t>-18,13; 81,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-36,23; 48,13</t>
+          <t>-40,08; 54,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-50,39; 71,5</t>
+          <t>-1,33; 113,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 89,05</t>
+          <t>-10,81; 88,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,08; 55,37</t>
+          <t>-29,51; 54,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 102,18</t>
+          <t>20,72; 132,14</t>
         </is>
       </c>
     </row>
@@ -1282,29 +1282,29 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>1,72</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1,42</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,93</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
           <t>1,79</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,42</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,39</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,79</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0,7</t>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,66</t>
+          <t>1,86</t>
         </is>
       </c>
     </row>
@@ -1325,37 +1325,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,95</t>
+          <t>0,73; 3,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 2,68</t>
+          <t>-0,19; 2,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,18</t>
+          <t>0,44; 3,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 3,71</t>
+          <t>-1,08; 3,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 2,6</t>
+          <t>-1,93; 2,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,59</t>
+          <t>-0,36; 3,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,27</t>
+          <t>0,3; 3,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,06</t>
+          <t>0,51; 3,19</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>100,08%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>40,58%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>22,71; 293,02</t>
+          <t>24,83; 318,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 217,67</t>
+          <t>-9,17; 224,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,97; 253,21</t>
+          <t>13,46; 251,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 61,96</t>
+          <t>-13,65; 59,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,38; 41,16</t>
+          <t>-23,77; 45,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 62,46</t>
+          <t>-4,57; 62,5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,63; 81,27</t>
+          <t>5,42; 83,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 51,62</t>
+          <t>-12,46; 53,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,09; 77,88</t>
+          <t>9,37; 81,83</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>1,29</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,87</t>
+          <t>0,16; 1,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,81</t>
+          <t>-0,63; 0,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,95</t>
+          <t>0,48; 2,13</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,26</t>
+          <t>0,64; 3,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,98</t>
+          <t>-0,59; 1,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,87</t>
+          <t>0,01; 2,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,21</t>
+          <t>0,67; 2,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 1,05</t>
+          <t>-0,27; 1,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,67</t>
+          <t>0,58; 1,89</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>29,67%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>9,23; 105,17</t>
+          <t>4,37; 99,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-24,77; 44,99</t>
+          <t>-26,38; 43,5</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9,6; 110,28</t>
+          <t>17,06; 113,62</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9,15; 56,31</t>
+          <t>8,78; 55,49</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 32,64</t>
+          <t>-8,42; 32,59</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 31,9</t>
+          <t>0,31; 41,59</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,34; 56,44</t>
+          <t>14,81; 56,27</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 26,14</t>
+          <t>-5,81; 29,43</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2,14; 41,75</t>
+          <t>11,7; 46,62</t>
         </is>
       </c>
     </row>
